--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אנה זק – ילד שמנת</v>
+        <v>ששון שאולוב – נווה הדרים</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%a0%d7%94-%d7%96%d7%a7-%d7%99%d7%9c%d7%93-%d7%a9%d7%9e%d7%a0%d7%aa/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%a9%d7%95%d7%9f-%d7%a9%d7%90%d7%95%d7%9c%d7%95%d7%91-%d7%a0%d7%95%d7%95%d7%94-%d7%94%d7%93%d7%a8%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>אנה זק עושה פופ ציני, נוצץ ומודע לעצמו, שמצליח לקחת דמות מאוד מוכרת מהתרבות הישראלית – הילד העשיר שחי באינסטגרם, ולהפוך אותה לקריקטורה קצבית וממכרת. הדמות בשיר היא לא אדם ספציפי  אלא טיפוס: בן עשירים, חי באסתטיקה של רשתות חברתיות,</v>
+        <v>ששון שאולוב הוא ממובילי הגל החדש של הפופ־המזרחי הרומנטי בישראל: מדובר בשירים שמבוססים פחות על תחכום מוזיקלי ויותר על רגש ישיר, פגיעות גברית והגשה “שבורה” כמעט במכוון. "נווה הדרים" הוא שיר אהבה טוטאלי, מוגזם, מתמסר ולפעמים אפילו מתבכיין, אבל בדיוק</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אנה זק – ילד שמנת</v>
+        <v>ששון שאולוב – נווה הדרים</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ששון שאולוב – נווה הדרים</v>
+        <v>עידו מלכה – טפטופים</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%a9%d7%95%d7%9f-%d7%a9%d7%90%d7%95%d7%9c%d7%95%d7%91-%d7%a0%d7%95%d7%95%d7%94-%d7%94%d7%93%d7%a8%d7%99%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%a2%d7%99%d7%93%d7%95-%d7%9e%d7%9c%d7%9b%d7%94-%d7%98%d7%a4%d7%98%d7%95%d7%a4%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>ששון שאולוב הוא ממובילי הגל החדש של הפופ־המזרחי הרומנטי בישראל: מדובר בשירים שמבוססים פחות על תחכום מוזיקלי ויותר על רגש ישיר, פגיעות גברית והגשה “שבורה” כמעט במכוון. "נווה הדרים" הוא שיר אהבה טוטאלי, מוגזם, מתמסר ולפעמים אפילו מתבכיין, אבל בדיוק</v>
+        <v>השיר "טפטופים” של עידו מלכה עובד קודם כול בזכות הניגודיות שבו – מצד אחד כאב רגשי ובלבול, מצד שני ביטים קלילים, משחקי מילים ופזמון שנתקע בראש. זה שיר על אובססיה רומנטית, תלות רגשית והתבגרות אחרי קשר סוער. “עברתי כבר את</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ששון שאולוב – נווה הדרים</v>
+        <v>עידו מלכה – טפטופים</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עידו מלכה – טפטופים</v>
+        <v>מתן לוי – ילדה אחת</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-10</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%99%d7%93%d7%95-%d7%9e%d7%9c%d7%9b%d7%94-%d7%98%d7%a4%d7%98%d7%95%d7%a4%d7%99%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%aa%d7%9f-%d7%9c%d7%95%d7%99-%d7%99%d7%9c%d7%93%d7%94-%d7%90%d7%97%d7%aa/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-10</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "טפטופים” של עידו מלכה עובד קודם כול בזכות הניגודיות שבו – מצד אחד כאב רגשי ובלבול, מצד שני ביטים קלילים, משחקי מילים ופזמון שנתקע בראש. זה שיר על אובססיה רומנטית, תלות רגשית והתבגרות אחרי קשר סוער. “עברתי כבר את</v>
+        <v>מתן לוי שר בלדת רוק על רעב להכרה, בריחה מהכאב ומחיר התהילה. הוא מצליח לשלב בין רגש אישי מאוד לבין הפקה גדולה ודרמטית, וזה מה שנותן לו כוח. השיר על ילדה שבאה משבר – “אמא כאן אבא שם כמה יש</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עידו מלכה – טפטופים</v>
+        <v>מתן לוי – ילדה אחת</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מתן לוי – ילדה אחת</v>
+        <v>אבבה – Mother</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%aa%d7%9f-%d7%9c%d7%95%d7%99-%d7%99%d7%9c%d7%93%d7%94-%d7%90%d7%97%d7%aa/</v>
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%91%d7%94-mother/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מתן לוי שר בלדת רוק על רעב להכרה, בריחה מהכאב ומחיר התהילה. הוא מצליח לשלב בין רגש אישי מאוד לבין הפקה גדולה ודרמטית, וזה מה שנותן לו כוח. השיר על ילדה שבאה משבר – “אמא כאן אבא שם כמה יש</v>
+        <v>השיר 'Mother” של אבבה AvevA הוא הרבה מעבר לבלדת נשמה. זה שיר קינה, תפילה, חיבוק ומחאה בו־זמנית.הוא מצליח לקחת כאב קולקטיבי של אימהות, של קהילה ושל טראומה מתמשכת ולהפוך אותו לחוויה מוזיקלית שיש בה גם חמלה וגם כוח רוחני. זה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,126 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מתן לוי – ילדה אחת</v>
+        <v>אבבה – Mother</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>עדן חסון – כל הברכה שלי</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="C3" t="str">
+        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%97%d7%a1%d7%95%d7%9f-%d7%9b%d7%9c-%d7%94%d7%91%d7%a8%d7%9b%d7%94-%d7%a9%d7%9c%d7%99/</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>"כל הברכה שלי” של עדן חסון הוא שיר אהבה ים תיכוני שנשען כמעט כולו על רגש ישיר ולא מתוחכם. הוא לא מנסה להיות פיוטי, מורכב או חדשני אלא להעביר תחושת אהבה טוטאלית, חמה ומנחמת בצורה הכי נגישה שיש. הפשטות הזאת</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>עדן חסון – כל הברכה שלי</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>יערה לוי – קיטשי</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="C4" t="str">
+        <v>https://yosmusic.com/%d7%99%d7%a2%d7%a8%d7%94-%d7%9c%d7%95%d7%99-%d7%a7%d7%99%d7%98%d7%a9%d7%99/</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>השיר "קיטשי” של יערה לוי הוא שיר פופ־מידטמפו שמצליח לעשות משהו עדין ומעניין: לקחת רגש שנתפס כ"מביך" או "נאיבי" – הרצון לרומנטיקה אמיתית, ולהפוך אותו להצהרה מודעת לעצמה. הוא לא צוחק על הקיטש, אבל גם לא נופל אליו לגמרי. במקום</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>יערה לוי – קיטשי</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>נועה קירל – הכי יפה כשטעים לך</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="C5" t="str">
+        <v>https://yosmusic.com/%d7%a0%d7%95%d7%a2%d7%94-%d7%a7%d7%99%d7%a8%d7%9c-%d7%94%d7%9b%d7%99-%d7%99%d7%a4%d7%94-%d7%9b%d7%a9%d7%98%d7%a2%d7%99%d7%9d-%d7%9c%d7%9a/</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v>נועה קירל דוהרת על פופ־דאנס קליל שעוסק בנושא טעון: יחסי נשים עם אוכל, משקל ודימוי גוף.כותבי השיר אינם  מטיפים ולא נכנסים לדרמה כבדה  אלא משתמשים בהומור, גרוב ואנרגיה צעירה כדי לדבר על חרדה מאוד יומיומית. זה שיר ביט דאנס קופצני,</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>נועה קירל – הכי יפה כשטעים לך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אבבה – Mother</v>
+        <v>מתן חסן (המסתערב) לא מפחד</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%91%d7%94-mother/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%aa%d7%9f-%d7%97%d7%a1%d7%9f-%d7%94%d7%9e%d7%a1%d7%aa%d7%a2%d7%a8%d7%91-%d7%9c%d7%90-%d7%9e%d7%a4%d7%97%d7%93/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר 'Mother” של אבבה AvevA הוא הרבה מעבר לבלדת נשמה. זה שיר קינה, תפילה, חיבוק ומחאה בו־זמנית.הוא מצליח לקחת כאב קולקטיבי של אימהות, של קהילה ושל טראומה מתמשכת ולהפוך אותו לחוויה מוזיקלית שיש בה גם חמלה וגם כוח רוחני. זה</v>
+        <v>המקדם של השיר – הפער בין הדימוי שממנו הגיע  “המסתערב במסכה”  לבין החשיפה הרגשית .של השיר עצמו. מצד שני: במקום שיר כוחני או הירואי, מתן חסן מביא בלדת פופ־ים־תיכונית שמבוססת על פגיעות, חרדה קיומית וחיפוש עצמי. זה שיר על אדם</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,126 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אבבה – Mother</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>עדן חסון – כל הברכה שלי</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%97%d7%a1%d7%95%d7%9f-%d7%9b%d7%9c-%d7%94%d7%91%d7%a8%d7%9b%d7%94-%d7%a9%d7%9c%d7%99/</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>"כל הברכה שלי” של עדן חסון הוא שיר אהבה ים תיכוני שנשען כמעט כולו על רגש ישיר ולא מתוחכם. הוא לא מנסה להיות פיוטי, מורכב או חדשני אלא להעביר תחושת אהבה טוטאלית, חמה ומנחמת בצורה הכי נגישה שיש. הפשטות הזאת</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>עדן חסון – כל הברכה שלי</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>יערה לוי – קיטשי</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="C4" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%a2%d7%a8%d7%94-%d7%9c%d7%95%d7%99-%d7%a7%d7%99%d7%98%d7%a9%d7%99/</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v>השיר "קיטשי” של יערה לוי הוא שיר פופ־מידטמפו שמצליח לעשות משהו עדין ומעניין: לקחת רגש שנתפס כ"מביך" או "נאיבי" – הרצון לרומנטיקה אמיתית, ולהפוך אותו להצהרה מודעת לעצמה. הוא לא צוחק על הקיטש, אבל גם לא נופל אליו לגמרי. במקום</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>יערה לוי – קיטשי</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>נועה קירל – הכי יפה כשטעים לך</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="C5" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%95%d7%a2%d7%94-%d7%a7%d7%99%d7%a8%d7%9c-%d7%94%d7%9b%d7%99-%d7%99%d7%a4%d7%94-%d7%9b%d7%a9%d7%98%d7%a2%d7%99%d7%9d-%d7%9c%d7%9a/</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v>נועה קירל דוהרת על פופ־דאנס קליל שעוסק בנושא טעון: יחסי נשים עם אוכל, משקל ודימוי גוף.כותבי השיר אינם  מטיפים ולא נכנסים לדרמה כבדה  אלא משתמשים בהומור, גרוב ואנרגיה צעירה כדי לדבר על חרדה מאוד יומיומית. זה שיר ביט דאנס קופצני,</v>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>נועה קירל – הכי יפה כשטעים לך</v>
+        <v>מתן חסן (המסתערב) לא מפחד</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מתן חסן (המסתערב) לא מפחד</v>
+        <v>אלדד ציטרין ואדר גולד – פורטרט</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-12</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%aa%d7%9f-%d7%97%d7%a1%d7%9f-%d7%94%d7%9e%d7%a1%d7%aa%d7%a2%d7%a8%d7%91-%d7%9c%d7%90-%d7%9e%d7%a4%d7%97%d7%93/</v>
+        <v>https://yosmusic.com/%d7%90%d7%9c%d7%93%d7%93-%d7%a6%d7%99%d7%98%d7%a8%d7%99%d7%9f-%d7%95%d7%90%d7%93%d7%a8-%d7%92%d7%95%d7%9c%d7%93-%d7%a4%d7%95%d7%a8%d7%98%d7%a8%d7%98/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-12</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>המקדם של השיר – הפער בין הדימוי שממנו הגיע  “המסתערב במסכה”  לבין החשיפה הרגשית .של השיר עצמו. מצד שני: במקום שיר כוחני או הירואי, מתן חסן מביא בלדת פופ־ים־תיכונית שמבוססת על פגיעות, חרדה קיומית וחיפוש עצמי. זה שיר על אדם</v>
+        <v>אדר גולד ואלדד ציטרין מבצעים בלדה מינורית שקטה ומכאיבה שעוסקת באחד מסוגי הגעגוע המורכבים ביותר: געגוע למישהו שכמעט לא הספקת להכיר. זה שיר על זיכרון חסר, על ניסיון לבנות דמות מתוך סיפורים, חפצים ורסיסי נוכחות. במקום להתאבל על מה שהיה,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מתן חסן (המסתערב) לא מפחד</v>
+        <v>אלדד ציטרין ואדר גולד – פורטרט</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אלדד ציטרין ואדר גולד – פורטרט</v>
+        <v>מאי טוויק – שישרפו הקנאים</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%9c%d7%93%d7%93-%d7%a6%d7%99%d7%98%d7%a8%d7%99%d7%9f-%d7%95%d7%90%d7%93%d7%a8-%d7%92%d7%95%d7%9c%d7%93-%d7%a4%d7%95%d7%a8%d7%98%d7%a8%d7%98/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%99-%d7%98%d7%95%d7%95%d7%99%d7%a7-%d7%a9%d7%99%d7%a9%d7%a8%d7%a4%d7%95-%d7%94%d7%a7%d7%a0%d7%90%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>אדר גולד ואלדד ציטרין מבצעים בלדה מינורית שקטה ומכאיבה שעוסקת באחד מסוגי הגעגוע המורכבים ביותר: געגוע למישהו שכמעט לא הספקת להכיר. זה שיר על זיכרון חסר, על ניסיון לבנות דמות מתוך סיפורים, חפצים ורסיסי נוכחות. במקום להתאבל על מה שהיה,</v>
+        <v>"שישרפו הקנאים" של מאי טוויק בנוי כמו מסלול רגשי שמתפתח בהדרגה – מבלדה אינטימית ושבורה אל התפרצות EDM רגשית, כמעט קתרזיס של כאב. זה לא רק שינוי מוזיקלי – המעברים עצמם הם חלק מהסיפור. הפתיחה יושבת על קול נמוך, כמעט</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אלדד ציטרין ואדר גולד – פורטרט</v>
+        <v>מאי טוויק – שישרפו הקנאים</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מאי טוויק – שישרפו הקנאים</v>
+        <v>עילי בוטנר והילדים החדשים – גם בנים בוכים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-13</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%90%d7%99-%d7%98%d7%95%d7%95%d7%99%d7%a7-%d7%a9%d7%99%d7%a9%d7%a8%d7%a4%d7%95-%d7%94%d7%a7%d7%a0%d7%90%d7%99%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%a2%d7%99%d7%9c%d7%99-%d7%91%d7%95%d7%98%d7%a0%d7%a8-%d7%95%d7%94%d7%99%d7%9c%d7%93%d7%99%d7%9d-%d7%94%d7%97%d7%93%d7%a9%d7%99%d7%9d-%d7%92%d7%9d-%d7%91%d7%a0%d7%99%d7%9d-%d7%91%d7%95%d7%9b%d7%99/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-13</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"שישרפו הקנאים" של מאי טוויק בנוי כמו מסלול רגשי שמתפתח בהדרגה – מבלדה אינטימית ושבורה אל התפרצות EDM רגשית, כמעט קתרזיס של כאב. זה לא רק שינוי מוזיקלי – המעברים עצמם הם חלק מהסיפור. הפתיחה יושבת על קול נמוך, כמעט</v>
+        <v>"גם בנים בוכים" של עילי בוטנר והילדים החדשים בנוי כפופ מלודי מידטמפו שמתפתח בהדרגה  לא דרך דרופ חד או התפרצות דרמטית, אלא דרך הצטברות רגשית איטית, כמעט קולנועית. זה שיר שנע כמו נסיעה לילית ארוכה: כביש פתוח, אורות חולפים, מחשבות</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מאי טוויק – שישרפו הקנאים</v>
+        <v>עילי בוטנר והילדים החדשים – גם בנים בוכים</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עילי בוטנר והילדים החדשים – גם בנים בוכים</v>
+        <v>שחר טבוך ומאיה דדון – הנסיך של רמת גן</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%99%d7%9c%d7%99-%d7%91%d7%95%d7%98%d7%a0%d7%a8-%d7%95%d7%94%d7%99%d7%9c%d7%93%d7%99%d7%9d-%d7%94%d7%97%d7%93%d7%a9%d7%99%d7%9d-%d7%92%d7%9d-%d7%91%d7%a0%d7%99%d7%9d-%d7%91%d7%95%d7%9b%d7%99/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%97%d7%a8-%d7%98%d7%91%d7%95%d7%9a-%d7%95%d7%9e%d7%90%d7%99%d7%94-%d7%93%d7%93%d7%95%d7%9f-%d7%94%d7%a0%d7%a1%d7%99%d7%9a-%d7%a9%d7%9c-%d7%a8%d7%9e%d7%aa-%d7%92%d7%9f/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"גם בנים בוכים" של עילי בוטנר והילדים החדשים בנוי כפופ מלודי מידטמפו שמתפתח בהדרגה  לא דרך דרופ חד או התפרצות דרמטית, אלא דרך הצטברות רגשית איטית, כמעט קולנועית. זה שיר שנע כמו נסיעה לילית ארוכה: כביש פתוח, אורות חולפים, מחשבות</v>
+        <v>הנסיך של רמת גן של שחר טבוך ומאיה דדון הוא פופ ים־תיכוני צבעוני, קאמפי ומודע לעצמו, שמצליח להפוך מעבר דירה לרמת גן למיתולוגיה פופית קטנה.זה שיר שלא מנסה להיות “עמוק”  אלא כריזמטי, מצחיק, פלרטטני ומאוד מודע לתרבות הרשת והטיקטוק. שחר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עילי בוטנר והילדים החדשים – גם בנים בוכים</v>
+        <v>שחר טבוך ומאיה דדון – הנסיך של רמת גן</v>
       </c>
     </row>
   </sheetData>
